--- a/public/assets/templates/operasional/esp.xlsx
+++ b/public/assets/templates/operasional/esp.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ThinkPad\Documents\MAGANG\PT BAS\ENG\Operasional\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\pt_bas\Engineering\public\assets\templates\operasional\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{456FDCEC-B76C-494D-83B7-C9D86AFBAD6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0574D7DA-30B0-403E-927C-B294199319D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10560" xr2:uid="{EDADF9A9-188A-488C-B753-4AC18A769DB7}"/>
   </bookViews>
@@ -149,7 +149,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7">
+  <fonts count="10">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -197,6 +197,29 @@
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -410,8 +433,143 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="60">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -427,150 +585,29 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="20" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="20" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -608,7 +645,7 @@
         <xdr:cNvPr id="2" name="Picture 1" descr="Logo PT.BAS">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4F54DBE1-804E-482F-AF84-A2862891EA61}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -657,7 +694,7 @@
                   <a14:compatExt spid="_x0000_s1025"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{03E3D777-147D-443F-ABB4-6C7DCDCD47B1}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -694,7 +731,7 @@
           <xdr:col>10</xdr:col>
           <xdr:colOff>247650</xdr:colOff>
           <xdr:row>6</xdr:row>
-          <xdr:rowOff>95250</xdr:rowOff>
+          <xdr:rowOff>101600</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -704,7 +741,7 @@
                   <a14:compatExt spid="_x0000_s1026"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E77CD59B-13B2-4609-9394-6E78089E8A90}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002040000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -751,7 +788,7 @@
                   <a14:compatExt spid="_x0000_s1027"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A3449B7A-4CC2-4FA4-8044-54E047AB11DB}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000003040000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -1075,7 +1112,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0934695C-63B7-478E-8476-11CE3472351A}">
-  <dimension ref="A1:K35"/>
+  <dimension ref="A1:K36"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5"/>
   <cols>
     <col min="2" max="3" width="16.81640625" customWidth="1"/>
@@ -1086,608 +1123,615 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="20">
-      <c r="A1" s="1"/>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="3" t="s">
+      <c r="A1" s="46"/>
+      <c r="B1" s="47"/>
+      <c r="C1" s="47"/>
+      <c r="D1" s="48" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
-      <c r="G1" s="3"/>
-      <c r="H1" s="3"/>
-      <c r="I1" s="3"/>
-      <c r="J1" s="4" t="s">
+      <c r="E1" s="48"/>
+      <c r="F1" s="48"/>
+      <c r="G1" s="48"/>
+      <c r="H1" s="48"/>
+      <c r="I1" s="48"/>
+      <c r="J1" s="49" t="s">
         <v>1</v>
       </c>
-      <c r="K1" s="5"/>
+      <c r="K1" s="50"/>
     </row>
     <row r="2" spans="1:11" ht="20">
-      <c r="A2" s="6"/>
-      <c r="B2" s="7"/>
-      <c r="C2" s="7"/>
-      <c r="D2" s="8" t="s">
+      <c r="A2" s="33"/>
+      <c r="B2" s="34"/>
+      <c r="C2" s="34"/>
+      <c r="D2" s="53" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="8"/>
-      <c r="F2" s="8"/>
-      <c r="G2" s="8"/>
-      <c r="H2" s="8"/>
-      <c r="I2" s="8"/>
-      <c r="J2" s="9"/>
-      <c r="K2" s="10"/>
+      <c r="E2" s="53"/>
+      <c r="F2" s="53"/>
+      <c r="G2" s="53"/>
+      <c r="H2" s="53"/>
+      <c r="I2" s="53"/>
+      <c r="J2" s="51"/>
+      <c r="K2" s="52"/>
     </row>
     <row r="3" spans="1:11">
-      <c r="A3" s="11"/>
-      <c r="B3" s="12"/>
-      <c r="C3" s="12"/>
-      <c r="D3" s="12"/>
-      <c r="E3" s="12"/>
-      <c r="F3" s="12"/>
-      <c r="G3" s="12"/>
-      <c r="H3" s="12"/>
-      <c r="I3" s="12"/>
-      <c r="J3" s="12"/>
-      <c r="K3" s="13"/>
+      <c r="A3" s="30"/>
+      <c r="B3" s="31"/>
+      <c r="C3" s="31"/>
+      <c r="D3" s="31"/>
+      <c r="E3" s="31"/>
+      <c r="F3" s="31"/>
+      <c r="G3" s="31"/>
+      <c r="H3" s="31"/>
+      <c r="I3" s="31"/>
+      <c r="J3" s="31"/>
+      <c r="K3" s="32"/>
     </row>
     <row r="4" spans="1:11" ht="15.5">
-      <c r="A4" s="14" t="s">
+      <c r="A4" s="45" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="15" t="s">
+      <c r="B4" s="42" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="15" t="s">
+      <c r="C4" s="42" t="s">
         <v>6</v>
       </c>
-      <c r="D4" s="15" t="s">
+      <c r="D4" s="42" t="s">
         <v>7</v>
       </c>
-      <c r="E4" s="15" t="s">
+      <c r="E4" s="42" t="s">
         <v>8</v>
       </c>
-      <c r="F4" s="15" t="s">
+      <c r="F4" s="42" t="s">
         <v>9</v>
       </c>
-      <c r="G4" s="16"/>
-      <c r="H4" s="17"/>
-      <c r="I4" s="15" t="s">
+      <c r="G4" s="1"/>
+      <c r="H4" s="2"/>
+      <c r="I4" s="42" t="s">
         <v>10</v>
       </c>
-      <c r="J4" s="15"/>
-      <c r="K4" s="18" t="s">
+      <c r="J4" s="42"/>
+      <c r="K4" s="3" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="15.5">
-      <c r="A5" s="14"/>
-      <c r="B5" s="15"/>
-      <c r="C5" s="15"/>
-      <c r="D5" s="15"/>
-      <c r="E5" s="15"/>
-      <c r="F5" s="15"/>
-      <c r="G5" s="16"/>
-      <c r="H5" s="19" t="s">
+      <c r="A5" s="45"/>
+      <c r="B5" s="42"/>
+      <c r="C5" s="42"/>
+      <c r="D5" s="42"/>
+      <c r="E5" s="42"/>
+      <c r="F5" s="42"/>
+      <c r="G5" s="1"/>
+      <c r="H5" s="39" t="s">
         <v>11</v>
       </c>
-      <c r="I5" s="17" t="s">
+      <c r="I5" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="J5" s="17"/>
-      <c r="K5" s="20"/>
+      <c r="J5" s="2"/>
+      <c r="K5" s="5"/>
     </row>
     <row r="6" spans="1:11" ht="15.5">
-      <c r="A6" s="21">
+      <c r="A6" s="6">
         <v>0.25</v>
       </c>
-      <c r="B6" s="22"/>
-      <c r="C6" s="22"/>
-      <c r="D6" s="22"/>
-      <c r="E6" s="22"/>
-      <c r="F6" s="22"/>
-      <c r="G6" s="23"/>
-      <c r="H6" s="19"/>
-      <c r="I6" s="17" t="s">
+      <c r="B6" s="7"/>
+      <c r="C6" s="7"/>
+      <c r="D6" s="7"/>
+      <c r="E6" s="7"/>
+      <c r="F6" s="7"/>
+      <c r="G6" s="8"/>
+      <c r="H6" s="39"/>
+      <c r="I6" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="J6" s="17"/>
-      <c r="K6" s="20"/>
+      <c r="J6" s="2"/>
+      <c r="K6" s="5"/>
     </row>
     <row r="7" spans="1:11" ht="30">
-      <c r="A7" s="21">
+      <c r="A7" s="6">
         <v>0.29166666666666702</v>
       </c>
-      <c r="B7" s="22"/>
-      <c r="C7" s="22"/>
-      <c r="D7" s="22"/>
-      <c r="E7" s="22"/>
-      <c r="F7" s="22"/>
-      <c r="G7" s="23"/>
-      <c r="H7" s="24" t="s">
+      <c r="B7" s="7"/>
+      <c r="C7" s="7"/>
+      <c r="D7" s="7"/>
+      <c r="E7" s="7"/>
+      <c r="F7" s="7"/>
+      <c r="G7" s="8"/>
+      <c r="H7" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="I7" s="25"/>
-      <c r="J7" s="25"/>
-      <c r="K7" s="20" t="s">
+      <c r="I7" s="40"/>
+      <c r="J7" s="40"/>
+      <c r="K7" s="5" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="8" spans="1:11" ht="30">
-      <c r="A8" s="21">
+      <c r="A8" s="6">
         <v>0.33333333333333298</v>
       </c>
-      <c r="B8" s="22"/>
-      <c r="C8" s="22"/>
-      <c r="D8" s="22"/>
-      <c r="E8" s="22"/>
-      <c r="F8" s="22"/>
-      <c r="G8" s="23"/>
-      <c r="H8" s="24" t="s">
+      <c r="B8" s="7"/>
+      <c r="C8" s="7"/>
+      <c r="D8" s="7"/>
+      <c r="E8" s="7"/>
+      <c r="F8" s="7"/>
+      <c r="G8" s="8"/>
+      <c r="H8" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="I8" s="25"/>
-      <c r="J8" s="25"/>
-      <c r="K8" s="20" t="s">
+      <c r="I8" s="40"/>
+      <c r="J8" s="40"/>
+      <c r="K8" s="5" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="15.5">
-      <c r="A9" s="21">
+      <c r="A9" s="6">
         <v>0.375</v>
       </c>
-      <c r="B9" s="22"/>
-      <c r="C9" s="22"/>
-      <c r="D9" s="22"/>
-      <c r="E9" s="22"/>
-      <c r="F9" s="22"/>
-      <c r="G9" s="23"/>
-      <c r="H9" s="24" t="s">
+      <c r="B9" s="7"/>
+      <c r="C9" s="7"/>
+      <c r="D9" s="7"/>
+      <c r="E9" s="7"/>
+      <c r="F9" s="7"/>
+      <c r="G9" s="8"/>
+      <c r="H9" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="I9" s="25"/>
-      <c r="J9" s="25"/>
-      <c r="K9" s="20"/>
+      <c r="I9" s="40"/>
+      <c r="J9" s="40"/>
+      <c r="K9" s="5"/>
     </row>
     <row r="10" spans="1:11" ht="15.5">
-      <c r="A10" s="21">
+      <c r="A10" s="6">
         <v>0.41666666666666702</v>
       </c>
-      <c r="B10" s="22"/>
-      <c r="C10" s="22"/>
-      <c r="D10" s="22"/>
-      <c r="E10" s="22"/>
-      <c r="F10" s="22"/>
-      <c r="G10" s="23"/>
-      <c r="H10" s="26"/>
-      <c r="I10" s="27" t="s">
+      <c r="B10" s="7"/>
+      <c r="C10" s="7"/>
+      <c r="D10" s="7"/>
+      <c r="E10" s="7"/>
+      <c r="F10" s="7"/>
+      <c r="G10" s="8"/>
+      <c r="H10" s="10"/>
+      <c r="I10" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="J10" s="27" t="s">
+      <c r="J10" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="K10" s="28"/>
+      <c r="K10" s="11"/>
     </row>
     <row r="11" spans="1:11" ht="15.5">
-      <c r="A11" s="21">
+      <c r="A11" s="6">
         <v>0.45833333333333298</v>
       </c>
-      <c r="B11" s="22"/>
-      <c r="C11" s="22"/>
-      <c r="D11" s="22"/>
-      <c r="E11" s="22"/>
-      <c r="F11" s="22"/>
-      <c r="G11" s="23"/>
-      <c r="H11" s="24" t="s">
+      <c r="B11" s="7"/>
+      <c r="C11" s="7"/>
+      <c r="D11" s="7"/>
+      <c r="E11" s="7"/>
+      <c r="F11" s="7"/>
+      <c r="G11" s="8"/>
+      <c r="H11" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="I11" s="29"/>
-      <c r="J11" s="29"/>
-      <c r="K11" s="20" t="s">
+      <c r="I11" s="12"/>
+      <c r="J11" s="12"/>
+      <c r="K11" s="5" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="12" spans="1:11" ht="30">
-      <c r="A12" s="21">
+      <c r="A12" s="6">
         <v>0.5</v>
       </c>
-      <c r="B12" s="22"/>
-      <c r="C12" s="22"/>
-      <c r="D12" s="22"/>
-      <c r="E12" s="22"/>
-      <c r="F12" s="22"/>
-      <c r="G12" s="23"/>
-      <c r="H12" s="24" t="s">
+      <c r="B12" s="7"/>
+      <c r="C12" s="7"/>
+      <c r="D12" s="7"/>
+      <c r="E12" s="7"/>
+      <c r="F12" s="7"/>
+      <c r="G12" s="8"/>
+      <c r="H12" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="I12" s="29"/>
-      <c r="J12" s="29"/>
-      <c r="K12" s="20"/>
+      <c r="I12" s="12"/>
+      <c r="J12" s="12"/>
+      <c r="K12" s="5"/>
     </row>
     <row r="13" spans="1:11" ht="30">
-      <c r="A13" s="21">
+      <c r="A13" s="6">
         <v>0.54166666666666696</v>
       </c>
-      <c r="B13" s="22"/>
-      <c r="C13" s="22"/>
-      <c r="D13" s="22"/>
-      <c r="E13" s="22"/>
-      <c r="F13" s="22"/>
-      <c r="G13" s="23"/>
-      <c r="H13" s="24" t="s">
+      <c r="B13" s="7"/>
+      <c r="C13" s="7"/>
+      <c r="D13" s="7"/>
+      <c r="E13" s="7"/>
+      <c r="F13" s="7"/>
+      <c r="G13" s="8"/>
+      <c r="H13" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="I13" s="30"/>
-      <c r="J13" s="31"/>
-      <c r="K13" s="20" t="s">
+      <c r="I13" s="37"/>
+      <c r="J13" s="38"/>
+      <c r="K13" s="5" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="14" spans="1:11">
-      <c r="A14" s="21">
+      <c r="A14" s="6">
         <v>0.58333333333333304</v>
       </c>
-      <c r="B14" s="22"/>
-      <c r="C14" s="22"/>
-      <c r="D14" s="22"/>
-      <c r="E14" s="22"/>
-      <c r="F14" s="22"/>
-      <c r="G14" s="23"/>
-      <c r="H14" s="19" t="s">
+      <c r="B14" s="7"/>
+      <c r="C14" s="7"/>
+      <c r="D14" s="7"/>
+      <c r="E14" s="7"/>
+      <c r="F14" s="7"/>
+      <c r="G14" s="8"/>
+      <c r="H14" s="39" t="s">
         <v>25</v>
       </c>
-      <c r="I14" s="25"/>
-      <c r="J14" s="25"/>
-      <c r="K14" s="32" t="s">
+      <c r="I14" s="40"/>
+      <c r="J14" s="40"/>
+      <c r="K14" s="41" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="15" spans="1:11">
-      <c r="A15" s="21">
+      <c r="A15" s="6">
         <v>0.625</v>
       </c>
-      <c r="B15" s="22"/>
-      <c r="C15" s="22"/>
-      <c r="D15" s="22"/>
-      <c r="E15" s="22"/>
-      <c r="F15" s="22"/>
-      <c r="G15" s="23"/>
-      <c r="H15" s="19"/>
-      <c r="I15" s="25"/>
-      <c r="J15" s="25"/>
-      <c r="K15" s="32"/>
+      <c r="B15" s="7"/>
+      <c r="C15" s="7"/>
+      <c r="D15" s="7"/>
+      <c r="E15" s="7"/>
+      <c r="F15" s="7"/>
+      <c r="G15" s="8"/>
+      <c r="H15" s="39"/>
+      <c r="I15" s="40"/>
+      <c r="J15" s="40"/>
+      <c r="K15" s="41"/>
     </row>
     <row r="16" spans="1:11" ht="15">
-      <c r="A16" s="21">
+      <c r="A16" s="6">
         <v>0.66666666666666696</v>
       </c>
-      <c r="B16" s="22"/>
-      <c r="C16" s="22"/>
-      <c r="D16" s="22"/>
-      <c r="E16" s="22"/>
-      <c r="F16" s="22"/>
-      <c r="G16" s="23"/>
-      <c r="H16" s="15" t="s">
+      <c r="B16" s="7"/>
+      <c r="C16" s="7"/>
+      <c r="D16" s="7"/>
+      <c r="E16" s="7"/>
+      <c r="F16" s="7"/>
+      <c r="G16" s="8"/>
+      <c r="H16" s="42" t="s">
         <v>26</v>
       </c>
-      <c r="I16" s="15"/>
-      <c r="J16" s="15"/>
-      <c r="K16" s="33"/>
+      <c r="I16" s="42"/>
+      <c r="J16" s="42"/>
+      <c r="K16" s="43"/>
     </row>
     <row r="17" spans="1:11" ht="45">
-      <c r="A17" s="21">
+      <c r="A17" s="6">
         <v>0.70833333333333304</v>
       </c>
-      <c r="B17" s="22"/>
-      <c r="C17" s="22"/>
-      <c r="D17" s="22"/>
-      <c r="E17" s="22"/>
-      <c r="F17" s="22"/>
-      <c r="G17" s="23"/>
-      <c r="H17" s="34" t="s">
+      <c r="B17" s="7"/>
+      <c r="C17" s="7"/>
+      <c r="D17" s="7"/>
+      <c r="E17" s="7"/>
+      <c r="F17" s="7"/>
+      <c r="G17" s="8"/>
+      <c r="H17" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="I17" s="24" t="s">
+      <c r="I17" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="J17" s="24" t="s">
+      <c r="J17" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="K17" s="35" t="s">
+      <c r="K17" s="14" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="18" spans="1:11">
-      <c r="A18" s="21">
+      <c r="A18" s="6">
         <v>0.75</v>
       </c>
-      <c r="B18" s="22"/>
-      <c r="C18" s="22"/>
-      <c r="D18" s="22"/>
-      <c r="E18" s="22"/>
-      <c r="F18" s="22"/>
-      <c r="G18" s="23"/>
-      <c r="H18" s="36" t="s">
+      <c r="B18" s="7"/>
+      <c r="C18" s="7"/>
+      <c r="D18" s="7"/>
+      <c r="E18" s="7"/>
+      <c r="F18" s="7"/>
+      <c r="G18" s="8"/>
+      <c r="H18" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="I18" s="22"/>
-      <c r="J18" s="22"/>
-      <c r="K18" s="37"/>
+      <c r="I18" s="7"/>
+      <c r="J18" s="7"/>
+      <c r="K18" s="16"/>
     </row>
     <row r="19" spans="1:11">
-      <c r="A19" s="21">
+      <c r="A19" s="6">
         <v>0.79166666666666696</v>
       </c>
-      <c r="B19" s="22"/>
-      <c r="C19" s="22"/>
-      <c r="D19" s="22"/>
-      <c r="E19" s="22"/>
-      <c r="F19" s="22"/>
-      <c r="G19" s="23"/>
-      <c r="H19" s="36" t="s">
+      <c r="B19" s="7"/>
+      <c r="C19" s="7"/>
+      <c r="D19" s="7"/>
+      <c r="E19" s="7"/>
+      <c r="F19" s="7"/>
+      <c r="G19" s="8"/>
+      <c r="H19" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="I19" s="22"/>
-      <c r="J19" s="22"/>
-      <c r="K19" s="37"/>
+      <c r="I19" s="7"/>
+      <c r="J19" s="7"/>
+      <c r="K19" s="16"/>
     </row>
     <row r="20" spans="1:11" ht="15.5">
-      <c r="A20" s="21">
+      <c r="A20" s="6">
         <v>0.83333333333333304</v>
       </c>
-      <c r="B20" s="22"/>
-      <c r="C20" s="22"/>
-      <c r="D20" s="22"/>
-      <c r="E20" s="22"/>
-      <c r="F20" s="22"/>
-      <c r="G20" s="23"/>
-      <c r="H20" s="38"/>
-      <c r="I20" s="39"/>
-      <c r="J20" s="39"/>
-      <c r="K20" s="40"/>
+      <c r="B20" s="7"/>
+      <c r="C20" s="7"/>
+      <c r="D20" s="7"/>
+      <c r="E20" s="7"/>
+      <c r="F20" s="7"/>
+      <c r="G20" s="8"/>
+      <c r="H20" s="17"/>
+      <c r="I20" s="44"/>
+      <c r="J20" s="44"/>
+      <c r="K20" s="18"/>
     </row>
     <row r="21" spans="1:11" ht="15">
-      <c r="A21" s="21">
+      <c r="A21" s="6">
         <v>0.875</v>
       </c>
-      <c r="B21" s="22"/>
-      <c r="C21" s="22"/>
-      <c r="D21" s="22"/>
-      <c r="E21" s="22"/>
-      <c r="F21" s="22"/>
-      <c r="G21" s="23"/>
-      <c r="H21" s="41"/>
-      <c r="I21" s="42"/>
-      <c r="J21" s="42"/>
-      <c r="K21" s="43"/>
+      <c r="B21" s="7"/>
+      <c r="C21" s="7"/>
+      <c r="D21" s="7"/>
+      <c r="E21" s="7"/>
+      <c r="F21" s="7"/>
+      <c r="G21" s="8"/>
+      <c r="H21" s="19"/>
+      <c r="I21" s="28"/>
+      <c r="J21" s="28"/>
+      <c r="K21" s="20"/>
     </row>
     <row r="22" spans="1:11" ht="15.5">
-      <c r="A22" s="21">
+      <c r="A22" s="6">
         <v>0.91666666666666696</v>
       </c>
-      <c r="B22" s="22"/>
-      <c r="C22" s="22"/>
-      <c r="D22" s="22"/>
-      <c r="E22" s="22"/>
-      <c r="F22" s="22"/>
-      <c r="G22" s="23"/>
-      <c r="H22" s="41"/>
-      <c r="I22" s="39"/>
-      <c r="J22" s="39"/>
-      <c r="K22" s="40"/>
+      <c r="B22" s="7"/>
+      <c r="C22" s="7"/>
+      <c r="D22" s="7"/>
+      <c r="E22" s="7"/>
+      <c r="F22" s="7"/>
+      <c r="G22" s="8"/>
+      <c r="H22" s="19"/>
+      <c r="I22" s="44"/>
+      <c r="J22" s="44"/>
+      <c r="K22" s="18"/>
     </row>
     <row r="23" spans="1:11" ht="15">
-      <c r="A23" s="21">
+      <c r="A23" s="6">
         <v>0.95833333333333304</v>
       </c>
-      <c r="B23" s="22"/>
-      <c r="C23" s="22"/>
-      <c r="D23" s="22"/>
-      <c r="E23" s="22"/>
-      <c r="F23" s="22"/>
-      <c r="G23" s="23"/>
-      <c r="H23" s="42"/>
-      <c r="I23" s="42"/>
-      <c r="J23" s="42"/>
-      <c r="K23" s="44"/>
+      <c r="B23" s="7"/>
+      <c r="C23" s="7"/>
+      <c r="D23" s="7"/>
+      <c r="E23" s="7"/>
+      <c r="F23" s="7"/>
+      <c r="G23" s="8"/>
+      <c r="H23" s="28"/>
+      <c r="I23" s="28"/>
+      <c r="J23" s="28"/>
+      <c r="K23" s="29"/>
     </row>
     <row r="24" spans="1:11" ht="15">
-      <c r="A24" s="21">
+      <c r="A24" s="6">
         <v>1</v>
       </c>
-      <c r="B24" s="22"/>
-      <c r="C24" s="22"/>
-      <c r="D24" s="22"/>
-      <c r="E24" s="22"/>
-      <c r="F24" s="22"/>
-      <c r="G24" s="23"/>
-      <c r="H24" s="45"/>
-      <c r="I24" s="45"/>
-      <c r="J24" s="45"/>
-      <c r="K24" s="46"/>
+      <c r="B24" s="7"/>
+      <c r="C24" s="7"/>
+      <c r="D24" s="7"/>
+      <c r="E24" s="7"/>
+      <c r="F24" s="7"/>
+      <c r="G24" s="8"/>
+      <c r="H24" s="21"/>
+      <c r="I24" s="21"/>
+      <c r="J24" s="21"/>
+      <c r="K24" s="22"/>
     </row>
     <row r="25" spans="1:11">
-      <c r="A25" s="21">
+      <c r="A25" s="6">
         <v>1.0416666666666701</v>
       </c>
-      <c r="B25" s="22"/>
-      <c r="C25" s="22"/>
-      <c r="D25" s="22"/>
-      <c r="E25" s="22"/>
-      <c r="F25" s="22"/>
-      <c r="G25" s="23"/>
-      <c r="H25" s="47"/>
-      <c r="I25" s="23"/>
-      <c r="J25" s="23"/>
-      <c r="K25" s="43"/>
+      <c r="B25" s="7"/>
+      <c r="C25" s="7"/>
+      <c r="D25" s="7"/>
+      <c r="E25" s="7"/>
+      <c r="F25" s="7"/>
+      <c r="G25" s="8"/>
+      <c r="H25" s="23"/>
+      <c r="I25" s="8"/>
+      <c r="J25" s="8"/>
+      <c r="K25" s="20"/>
     </row>
     <row r="26" spans="1:11">
-      <c r="A26" s="21">
+      <c r="A26" s="6">
         <v>1.0833333333333299</v>
       </c>
-      <c r="B26" s="22"/>
-      <c r="C26" s="22"/>
-      <c r="D26" s="22"/>
-      <c r="E26" s="22"/>
-      <c r="F26" s="22"/>
-      <c r="G26" s="23"/>
-      <c r="H26" s="47"/>
-      <c r="I26" s="23"/>
-      <c r="J26" s="23"/>
-      <c r="K26" s="43"/>
+      <c r="B26" s="7"/>
+      <c r="C26" s="7"/>
+      <c r="D26" s="7"/>
+      <c r="E26" s="7"/>
+      <c r="F26" s="7"/>
+      <c r="G26" s="8"/>
+      <c r="H26" s="23"/>
+      <c r="I26" s="8"/>
+      <c r="J26" s="8"/>
+      <c r="K26" s="20"/>
     </row>
     <row r="27" spans="1:11">
-      <c r="A27" s="21">
+      <c r="A27" s="6">
         <v>1.125</v>
       </c>
-      <c r="B27" s="22"/>
-      <c r="C27" s="22"/>
-      <c r="D27" s="22"/>
-      <c r="E27" s="22"/>
-      <c r="F27" s="22"/>
-      <c r="G27" s="23"/>
-      <c r="H27" s="23"/>
-      <c r="I27" s="23"/>
-      <c r="J27" s="23"/>
-      <c r="K27" s="43"/>
+      <c r="B27" s="7"/>
+      <c r="C27" s="7"/>
+      <c r="D27" s="7"/>
+      <c r="E27" s="7"/>
+      <c r="F27" s="7"/>
+      <c r="G27" s="8"/>
+      <c r="H27" s="8"/>
+      <c r="I27" s="8"/>
+      <c r="J27" s="8"/>
+      <c r="K27" s="20"/>
     </row>
     <row r="28" spans="1:11">
-      <c r="A28" s="21">
+      <c r="A28" s="6">
         <v>1.1666666666666701</v>
       </c>
-      <c r="B28" s="22"/>
-      <c r="C28" s="22"/>
-      <c r="D28" s="22"/>
-      <c r="E28" s="22"/>
-      <c r="F28" s="22"/>
-      <c r="G28" s="23"/>
-      <c r="H28" s="23"/>
-      <c r="I28" s="23"/>
-      <c r="J28" s="23"/>
-      <c r="K28" s="43"/>
+      <c r="B28" s="7"/>
+      <c r="C28" s="7"/>
+      <c r="D28" s="7"/>
+      <c r="E28" s="7"/>
+      <c r="F28" s="7"/>
+      <c r="G28" s="8"/>
+      <c r="H28" s="8"/>
+      <c r="I28" s="8"/>
+      <c r="J28" s="8"/>
+      <c r="K28" s="20"/>
     </row>
     <row r="29" spans="1:11">
-      <c r="A29" s="21">
+      <c r="A29" s="6">
         <v>1.2083333333333299</v>
       </c>
-      <c r="B29" s="22"/>
-      <c r="C29" s="22"/>
-      <c r="D29" s="22"/>
-      <c r="E29" s="22"/>
-      <c r="F29" s="22"/>
-      <c r="G29" s="23"/>
-      <c r="H29" s="23"/>
-      <c r="I29" s="23"/>
-      <c r="J29" s="23"/>
-      <c r="K29" s="43"/>
+      <c r="B29" s="7"/>
+      <c r="C29" s="7"/>
+      <c r="D29" s="7"/>
+      <c r="E29" s="7"/>
+      <c r="F29" s="7"/>
+      <c r="G29" s="8"/>
+      <c r="H29" s="8"/>
+      <c r="I29" s="8"/>
+      <c r="J29" s="8"/>
+      <c r="K29" s="20"/>
     </row>
     <row r="30" spans="1:11">
-      <c r="A30" s="11"/>
-      <c r="B30" s="12"/>
-      <c r="C30" s="12"/>
-      <c r="D30" s="12"/>
-      <c r="E30" s="12"/>
-      <c r="F30" s="12"/>
-      <c r="G30" s="12"/>
-      <c r="H30" s="12"/>
-      <c r="I30" s="12"/>
-      <c r="J30" s="12"/>
-      <c r="K30" s="13"/>
+      <c r="A30" s="30"/>
+      <c r="B30" s="31"/>
+      <c r="C30" s="31"/>
+      <c r="D30" s="31"/>
+      <c r="E30" s="31"/>
+      <c r="F30" s="31"/>
+      <c r="G30" s="31"/>
+      <c r="H30" s="31"/>
+      <c r="I30" s="31"/>
+      <c r="J30" s="31"/>
+      <c r="K30" s="32"/>
     </row>
     <row r="31" spans="1:11">
-      <c r="A31" s="6" t="s">
+      <c r="A31" s="33" t="s">
         <v>33</v>
       </c>
-      <c r="B31" s="7"/>
-      <c r="C31" s="7"/>
-      <c r="D31" s="48" t="s">
+      <c r="B31" s="34"/>
+      <c r="C31" s="34"/>
+      <c r="D31" s="35" t="s">
         <v>34</v>
       </c>
-      <c r="E31" s="48"/>
-      <c r="F31" s="48"/>
-      <c r="G31" s="48"/>
-      <c r="H31" s="7" t="s">
+      <c r="E31" s="35"/>
+      <c r="F31" s="35"/>
+      <c r="G31" s="35"/>
+      <c r="H31" s="34" t="s">
         <v>35</v>
       </c>
-      <c r="I31" s="7"/>
-      <c r="J31" s="7"/>
-      <c r="K31" s="49"/>
+      <c r="I31" s="34"/>
+      <c r="J31" s="34"/>
+      <c r="K31" s="36"/>
     </row>
     <row r="32" spans="1:11">
-      <c r="A32" s="6"/>
-      <c r="B32" s="7"/>
-      <c r="C32" s="7"/>
-      <c r="D32" s="7"/>
-      <c r="E32" s="7"/>
-      <c r="F32" s="7"/>
-      <c r="G32" s="7"/>
-      <c r="H32" s="7"/>
-      <c r="I32" s="7"/>
-      <c r="J32" s="7"/>
-      <c r="K32" s="49"/>
+      <c r="A32" s="33"/>
+      <c r="B32" s="34"/>
+      <c r="C32" s="34"/>
+      <c r="D32" s="34"/>
+      <c r="E32" s="34"/>
+      <c r="F32" s="34"/>
+      <c r="G32" s="34"/>
+      <c r="H32" s="34"/>
+      <c r="I32" s="34"/>
+      <c r="J32" s="34"/>
+      <c r="K32" s="36"/>
     </row>
     <row r="33" spans="1:11">
-      <c r="A33" s="6"/>
-      <c r="B33" s="7"/>
-      <c r="C33" s="7"/>
-      <c r="D33" s="7"/>
-      <c r="E33" s="7"/>
-      <c r="F33" s="7"/>
-      <c r="G33" s="7"/>
-      <c r="H33" s="7"/>
-      <c r="I33" s="7"/>
-      <c r="J33" s="7"/>
-      <c r="K33" s="49"/>
+      <c r="A33" s="33"/>
+      <c r="B33" s="34"/>
+      <c r="C33" s="34"/>
+      <c r="D33" s="34"/>
+      <c r="E33" s="34"/>
+      <c r="F33" s="34"/>
+      <c r="G33" s="34"/>
+      <c r="H33" s="34"/>
+      <c r="I33" s="34"/>
+      <c r="J33" s="34"/>
+      <c r="K33" s="36"/>
     </row>
     <row r="34" spans="1:11">
-      <c r="A34" s="6"/>
-      <c r="B34" s="7"/>
-      <c r="C34" s="7"/>
-      <c r="D34" s="7"/>
-      <c r="E34" s="7"/>
-      <c r="F34" s="7"/>
-      <c r="G34" s="7"/>
-      <c r="H34" s="7"/>
-      <c r="I34" s="7"/>
-      <c r="J34" s="7"/>
-      <c r="K34" s="49"/>
-    </row>
-    <row r="35" spans="1:11" ht="15" thickBot="1">
-      <c r="A35" s="50" t="s">
+      <c r="A34" s="33"/>
+      <c r="B34" s="34"/>
+      <c r="C34" s="34"/>
+      <c r="D34" s="34"/>
+      <c r="E34" s="34"/>
+      <c r="F34" s="34"/>
+      <c r="G34" s="34"/>
+      <c r="H34" s="34"/>
+      <c r="I34" s="34"/>
+      <c r="J34" s="34"/>
+      <c r="K34" s="36"/>
+    </row>
+    <row r="35" spans="1:11" s="54" customFormat="1" ht="15" thickBot="1">
+      <c r="A35" s="24" t="s">
         <v>36</v>
       </c>
-      <c r="B35" s="51"/>
-      <c r="C35" s="51"/>
-      <c r="D35" s="52" t="s">
+      <c r="B35" s="25"/>
+      <c r="C35" s="25"/>
+      <c r="D35" s="26" t="s">
         <v>37</v>
       </c>
-      <c r="E35" s="52"/>
-      <c r="F35" s="52"/>
-      <c r="G35" s="52"/>
-      <c r="H35" s="51" t="s">
+      <c r="E35" s="26"/>
+      <c r="F35" s="26"/>
+      <c r="G35" s="26"/>
+      <c r="H35" s="25" t="s">
         <v>38</v>
       </c>
-      <c r="I35" s="51"/>
-      <c r="J35" s="51"/>
-      <c r="K35" s="53"/>
+      <c r="I35" s="25"/>
+      <c r="J35" s="25"/>
+      <c r="K35" s="27"/>
+    </row>
+    <row r="36" spans="1:11" s="59" customFormat="1" ht="15" thickBot="1">
+      <c r="A36" s="55"/>
+      <c r="B36" s="56"/>
+      <c r="C36" s="56"/>
+      <c r="D36" s="57"/>
+      <c r="E36" s="57"/>
+      <c r="F36" s="57"/>
+      <c r="G36" s="57"/>
+      <c r="H36" s="56"/>
+      <c r="I36" s="56"/>
+      <c r="J36" s="56"/>
+      <c r="K36" s="58"/>
     </row>
   </sheetData>
-  <mergeCells count="35">
-    <mergeCell ref="A35:C35"/>
-    <mergeCell ref="D35:G35"/>
-    <mergeCell ref="H35:K35"/>
-    <mergeCell ref="H23:K23"/>
-    <mergeCell ref="A30:K30"/>
-    <mergeCell ref="A31:C31"/>
-    <mergeCell ref="D31:G31"/>
-    <mergeCell ref="H31:K31"/>
-    <mergeCell ref="A32:C34"/>
-    <mergeCell ref="D32:G34"/>
-    <mergeCell ref="H32:K34"/>
-    <mergeCell ref="I13:J13"/>
-    <mergeCell ref="H14:H15"/>
-    <mergeCell ref="I14:J15"/>
-    <mergeCell ref="K14:K15"/>
-    <mergeCell ref="H16:K16"/>
+  <mergeCells count="38">
+    <mergeCell ref="A1:C2"/>
+    <mergeCell ref="D1:I1"/>
+    <mergeCell ref="J1:K2"/>
+    <mergeCell ref="D2:I2"/>
+    <mergeCell ref="A3:K3"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="E4:E5"/>
     <mergeCell ref="I20:J20"/>
     <mergeCell ref="I21:J21"/>
     <mergeCell ref="I22:J22"/>
@@ -1697,16 +1741,25 @@
     <mergeCell ref="I7:J7"/>
     <mergeCell ref="I8:J8"/>
     <mergeCell ref="I9:J9"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="D4:D5"/>
-    <mergeCell ref="E4:E5"/>
-    <mergeCell ref="A1:C2"/>
-    <mergeCell ref="D1:I1"/>
-    <mergeCell ref="J1:K2"/>
-    <mergeCell ref="D2:I2"/>
-    <mergeCell ref="A3:K3"/>
+    <mergeCell ref="I13:J13"/>
+    <mergeCell ref="H14:H15"/>
+    <mergeCell ref="I14:J15"/>
+    <mergeCell ref="K14:K15"/>
+    <mergeCell ref="H16:K16"/>
+    <mergeCell ref="A36:C36"/>
+    <mergeCell ref="D36:G36"/>
+    <mergeCell ref="H36:K36"/>
+    <mergeCell ref="H23:K23"/>
+    <mergeCell ref="A30:K30"/>
+    <mergeCell ref="A31:C31"/>
+    <mergeCell ref="D31:G31"/>
+    <mergeCell ref="H31:K31"/>
+    <mergeCell ref="A32:C34"/>
+    <mergeCell ref="D32:G34"/>
+    <mergeCell ref="H32:K34"/>
+    <mergeCell ref="A35:C35"/>
+    <mergeCell ref="D35:G35"/>
+    <mergeCell ref="H35:K35"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
